--- a/www/terminologies/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240426120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-26T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -427,6 +427,12 @@
   </si>
   <si>
     <t>Conseiller conjugal et familial</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Maîtrise du Facile à Lire et à Comprendre (FALC)</t>
   </si>
   <si>
     <t/>
@@ -697,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1157,15 +1163,23 @@
         <v>138</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>140</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,6 +433,12 @@
   </si>
   <si>
     <t>Maîtrise du Facile à Lire et à Comprendre (FALC)</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>Maitrise des outils informatisés à commande oculaire</t>
   </si>
   <si>
     <t/>
@@ -703,7 +709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1171,15 +1177,23 @@
         <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>142</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J33-CompetenceSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,12 +433,6 @@
   </si>
   <si>
     <t>Maîtrise du Facile à Lire et à Comprendre (FALC)</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>Maitrise des outils informatisés à commande oculaire</t>
   </si>
   <si>
     <t/>
@@ -709,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1177,23 +1171,15 @@
         <v>140</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>142</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
